--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435053.663652225</v>
+        <v>435054</v>
       </c>
       <c r="R2" t="n">
-        <v>6173012.518218987</v>
+        <v>6173013</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2004-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-04-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63117090</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63117090</v>
+        <v>74234136</v>
       </c>
       <c r="B2" t="n">
-        <v>104137</v>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50m S Koneho, Sk</t>
+          <t>Djurröd, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435054</v>
+        <v>435130</v>
       </c>
       <c r="R2" t="n">
-        <v>6173013</v>
+        <v>6173025</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-04-11</t>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Daphne mezereum/2D5g0944/Andrarum s:n/BeN/ /Bengt Nilsson,Sölvesborg</t>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,62 +785,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>granskog, ca 10 ex</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    924891</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Rune Gerell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74234309</v>
+        <v>74234137</v>
       </c>
       <c r="B3" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,14 +851,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djurröd, Skåne, Sk</t>
+          <t>Djurröd, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434976.0884982477</v>
+        <v>434976</v>
       </c>
       <c r="R3" t="n">
-        <v>6172809.119927151</v>
+        <v>6172809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -922,42 +927,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74234130</v>
+        <v>74234352</v>
       </c>
       <c r="B4" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>100085</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Bechsteins fladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis bechsteinii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,14 +977,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djurröd, Sk</t>
+          <t>Djurröd, Skåne, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434976.0884982477</v>
+        <v>435130</v>
       </c>
       <c r="R4" t="n">
-        <v>6172809.119927151</v>
+        <v>6173025</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1053,42 +1053,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74234288</v>
+        <v>74234335</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>100087</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1112,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434976.0884982477</v>
+        <v>435130</v>
       </c>
       <c r="R5" t="n">
-        <v>6172809.119927151</v>
+        <v>6173025</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1142,7 +1137,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1152,7 +1147,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1184,15 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74234357</v>
+        <v>74234309</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,26 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1243,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434976.0884982477</v>
+        <v>434976</v>
       </c>
       <c r="R6" t="n">
-        <v>6172809.119927151</v>
+        <v>6172809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1315,32 +1305,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74234278</v>
+        <v>74234317</v>
       </c>
       <c r="B7" t="n">
-        <v>57482</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1350,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1374,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434976.0884982477</v>
+        <v>435130</v>
       </c>
       <c r="R7" t="n">
-        <v>6172809.119927151</v>
+        <v>6173025</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1404,7 +1389,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1414,7 +1399,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1446,42 +1431,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74234339</v>
+        <v>74234348</v>
       </c>
       <c r="B8" t="n">
-        <v>57492</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205991</v>
+        <v>102102</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större musöra</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis myotis</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1797)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1505,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434976.0884982477</v>
+        <v>435130</v>
       </c>
       <c r="R8" t="n">
-        <v>6172809.119927151</v>
+        <v>6173025</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1535,7 +1515,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1545,7 +1525,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1574,6 +1554,1256 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>74234338</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56824</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205991</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större musöra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Myotis myotis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1797)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>435130</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6173025</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74234339</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56824</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205991</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Större musöra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Myotis myotis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1797)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6172809</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>74234356</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>435130</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6173025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74234357</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6172809</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74234146</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>435130</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6173025</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>74234147</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6172809</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74234303</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>435130</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6173025</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74234129</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>435130</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6173025</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74234130</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6172809</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>63117090</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>50m S Koneho, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>435054</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6173013</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2004-04-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2004-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum/2D5g0944/Andrarum s:n/BeN/ /Bengt Nilsson,Sölvesborg</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>granskog, ca 10 ex</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>SkFlora    924891</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32389-2023 artfynd.xlsx
+++ b/artfynd/A 32389-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234317</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1554,6 +1589,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1720,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234338</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2058,6 +2113,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234357</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2184,6 +2244,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234146</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2310,6 +2375,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234147</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2436,6 +2506,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2562,6 +2637,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234129</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2688,6 +2768,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234130</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2804,8 +2889,32 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63117090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>